--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.00230042368563</v>
+      </c>
+      <c r="C2">
         <v>29.10691146280739</v>
-      </c>
-      <c r="C2">
-        <v>24.00230042368563</v>
       </c>
       <c r="D2">
         <v>3.435610134307081</v>
       </c>
       <c r="E2">
-        <v>19.01055534423735</v>
+        <v>15.67658805629516</v>
       </c>
       <c r="F2">
         <v>65.31285659946748</v>
       </c>
       <c r="G2">
-        <v>15.67658805629517</v>
+        <v>19.01055534423735</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.39202550979394</v>
+      </c>
+      <c r="C3">
         <v>24.20884803987245</v>
-      </c>
-      <c r="C3">
-        <v>30.39202550979394</v>
       </c>
       <c r="D3">
         <v>4.130721124578007</v>
       </c>
       <c r="E3">
-        <v>15.65893353901084</v>
+        <v>19.65837890303403</v>
       </c>
       <c r="F3">
         <v>64.68268755795512</v>
       </c>
       <c r="G3">
-        <v>19.65837890303403</v>
+        <v>15.65893353901084</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>26.84567221687078</v>
+      </c>
+      <c r="C4">
         <v>26.63065914407596</v>
-      </c>
-      <c r="C4">
-        <v>26.84567221687078</v>
       </c>
       <c r="D4">
         <v>3.755070404340525</v>
       </c>
       <c r="E4">
-        <v>17.35163911459793</v>
+        <v>17.49173437937798</v>
       </c>
       <c r="F4">
         <v>65.1566265060241</v>
       </c>
       <c r="G4">
-        <v>17.49173437937798</v>
+        <v>17.35163911459793</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.60040567951319</v>
+      </c>
+      <c r="C5">
         <v>38.85161491652364</v>
-      </c>
-      <c r="C5">
-        <v>28.60040567951319</v>
       </c>
       <c r="D5">
         <v>2.573895582329317</v>
       </c>
       <c r="E5">
-        <v>23.20163995527395</v>
+        <v>17.07976146105106</v>
       </c>
       <c r="F5">
         <v>59.71859858367498</v>
       </c>
       <c r="G5">
-        <v>17.07976146105106</v>
+        <v>23.20163995527395</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.0623775516653</v>
+      </c>
+      <c r="C6">
         <v>25.51349301649498</v>
-      </c>
-      <c r="C6">
-        <v>31.0623775516653</v>
       </c>
       <c r="D6">
         <v>3.919494674263067</v>
       </c>
       <c r="E6">
-        <v>16.29465186680121</v>
+        <v>19.83854692230071</v>
       </c>
       <c r="F6">
         <v>63.86680121089808</v>
       </c>
       <c r="G6">
-        <v>19.83854692230071</v>
+        <v>16.29465186680121</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.3154486286954</v>
+      </c>
+      <c r="C7">
         <v>29.98413366577081</v>
-      </c>
-      <c r="C7">
-        <v>26.3154486286954</v>
       </c>
       <c r="D7">
         <v>3.335097192224622</v>
       </c>
       <c r="E7">
+        <v>16.83654443753884</v>
+      </c>
+      <c r="F7">
+        <v>63.97969753470063</v>
+      </c>
+      <c r="G7">
         <v>19.18375802776051</v>
-      </c>
-      <c r="F7">
-        <v>63.97969753470065</v>
-      </c>
-      <c r="G7">
-        <v>16.83654443753884</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.79425443730819</v>
+      </c>
+      <c r="C8">
         <v>28.66770019299522</v>
-      </c>
-      <c r="C8">
-        <v>28.79425443730819</v>
       </c>
       <c r="D8">
         <v>3.488246330427105</v>
       </c>
       <c r="E8">
-        <v>18.20611223854207</v>
+        <v>18.28648355401957</v>
       </c>
       <c r="F8">
         <v>63.50740420743837</v>
       </c>
       <c r="G8">
-        <v>18.28648355401957</v>
+        <v>18.20611223854207</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.78955954323002</v>
+      </c>
+      <c r="C9">
         <v>21.15811551717794</v>
-      </c>
-      <c r="C9">
-        <v>32.78955954323002</v>
       </c>
       <c r="D9">
         <v>4.72631884057971</v>
       </c>
       <c r="E9">
-        <v>13.74370578112053</v>
+        <v>21.29915864618523</v>
       </c>
       <c r="F9">
         <v>64.95713557269424</v>
       </c>
       <c r="G9">
-        <v>21.29915864618523</v>
+        <v>13.74370578112053</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.28944618599791</v>
+      </c>
+      <c r="C10">
         <v>31.41065830721003</v>
-      </c>
-      <c r="C10">
-        <v>29.28944618599791</v>
       </c>
       <c r="D10">
         <v>3.183632734530938</v>
       </c>
       <c r="E10">
-        <v>19.54613433903375</v>
+        <v>18.22615254567917</v>
       </c>
       <c r="F10">
         <v>62.22771311528707</v>
       </c>
       <c r="G10">
-        <v>18.22615254567917</v>
+        <v>19.54613433903375</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.98277008836664</v>
+      </c>
+      <c r="C11">
         <v>29.51466970723931</v>
-      </c>
-      <c r="C11">
-        <v>27.98277008836664</v>
       </c>
       <c r="D11">
         <v>3.388145657461726</v>
       </c>
       <c r="E11">
-        <v>18.73977745006033</v>
+        <v>17.7671269607186</v>
       </c>
       <c r="F11">
         <v>63.49309558922108</v>
       </c>
       <c r="G11">
-        <v>17.7671269607186</v>
+        <v>18.73977745006033</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.02461468977587</v>
+      </c>
+      <c r="C12">
         <v>32.53260317281093</v>
-      </c>
-      <c r="C12">
-        <v>28.02461468977587</v>
       </c>
       <c r="D12">
         <v>3.073839479392625</v>
       </c>
       <c r="E12">
-        <v>20.2623112220679</v>
+        <v>17.45459659979958</v>
       </c>
       <c r="F12">
         <v>62.28309217813252</v>
       </c>
       <c r="G12">
-        <v>17.45459659979958</v>
+        <v>20.2623112220679</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.40589120278723</v>
+      </c>
+      <c r="C13">
         <v>27.37984005067701</v>
-      </c>
-      <c r="C13">
-        <v>26.40589120278723</v>
       </c>
       <c r="D13">
         <v>3.652322285846492</v>
       </c>
       <c r="E13">
+        <v>17.17057297030111</v>
+      </c>
+      <c r="F13">
+        <v>65.02553857560655</v>
+      </c>
+      <c r="G13">
         <v>17.80388845409235</v>
-      </c>
-      <c r="F13">
-        <v>65.02553857560653</v>
-      </c>
-      <c r="G13">
-        <v>17.17057297030111</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>31.8523417302952</v>
+      </c>
+      <c r="C14">
         <v>26.5736788312391</v>
-      </c>
-      <c r="C14">
-        <v>31.8523417302952</v>
       </c>
       <c r="D14">
         <v>3.763122171945701</v>
       </c>
       <c r="E14">
-        <v>16.77355698075974</v>
+        <v>20.10549884254867</v>
       </c>
       <c r="F14">
         <v>63.12094417669159</v>
       </c>
       <c r="G14">
-        <v>20.10549884254867</v>
+        <v>16.77355698075974</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>30.30074241852271</v>
+      </c>
+      <c r="C15">
         <v>25.22964640744935</v>
-      </c>
-      <c r="C15">
-        <v>30.30074241852271</v>
       </c>
       <c r="D15">
         <v>3.96359102244389</v>
       </c>
       <c r="E15">
-        <v>16.22168284789644</v>
+        <v>19.48220064724919</v>
       </c>
       <c r="F15">
         <v>64.29611650485437</v>
       </c>
       <c r="G15">
-        <v>19.48220064724919</v>
+        <v>16.22168284789644</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>37.03246207816592</v>
+      </c>
+      <c r="C16">
         <v>28.54390039033549</v>
-      </c>
-      <c r="C16">
-        <v>37.03246207816592</v>
       </c>
       <c r="D16">
         <v>3.503375454388091</v>
       </c>
       <c r="E16">
+        <v>22.36579033750112</v>
+      </c>
+      <c r="F16">
+        <v>60.39509414819015</v>
+      </c>
+      <c r="G16">
         <v>17.23911551430873</v>
-      </c>
-      <c r="F16">
-        <v>60.39509414819014</v>
-      </c>
-      <c r="G16">
-        <v>22.36579033750112</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.8317185109638</v>
+      </c>
+      <c r="C17">
         <v>31.59102498725141</v>
-      </c>
-      <c r="C17">
-        <v>29.8317185109638</v>
       </c>
       <c r="D17">
         <v>3.16545601291364</v>
       </c>
       <c r="E17">
+        <v>18.48049281314168</v>
+      </c>
+      <c r="F17">
+        <v>61.94913915653134</v>
+      </c>
+      <c r="G17">
         <v>19.57036803032696</v>
-      </c>
-      <c r="F17">
-        <v>61.94913915653135</v>
-      </c>
-      <c r="G17">
-        <v>18.48049281314168</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.12066419012666</v>
+      </c>
+      <c r="C18">
         <v>26.69739963299467</v>
-      </c>
-      <c r="C18">
-        <v>28.12066419012666</v>
       </c>
       <c r="D18">
         <v>3.745683151718357</v>
       </c>
       <c r="E18">
-        <v>17.24436992281229</v>
+        <v>18.16368419531092</v>
       </c>
       <c r="F18">
         <v>64.59194588187678</v>
       </c>
       <c r="G18">
-        <v>18.16368419531092</v>
+        <v>17.24436992281229</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>34.57767448616458</v>
+      </c>
+      <c r="C19">
         <v>24.42443169438594</v>
-      </c>
-      <c r="C19">
-        <v>34.57767448616458</v>
       </c>
       <c r="D19">
         <v>4.094261076419863</v>
       </c>
       <c r="E19">
+        <v>21.74667702005208</v>
+      </c>
+      <c r="F19">
+        <v>62.89224866395652</v>
+      </c>
+      <c r="G19">
         <v>15.36107431599141</v>
-      </c>
-      <c r="F19">
-        <v>62.89224866395651</v>
-      </c>
-      <c r="G19">
-        <v>21.74667702005207</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>37.42532855436082</v>
+      </c>
+      <c r="C20">
         <v>23.13321385902031</v>
-      </c>
-      <c r="C20">
-        <v>37.42532855436082</v>
       </c>
       <c r="D20">
         <v>4.322788896061976</v>
       </c>
       <c r="E20">
-        <v>14.40796205004185</v>
+        <v>23.30945958515487</v>
       </c>
       <c r="F20">
         <v>62.28257836480327</v>
       </c>
       <c r="G20">
-        <v>23.30945958515487</v>
+        <v>14.40796205004185</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>30.57000619490823</v>
+      </c>
+      <c r="C21">
         <v>24.35121397810137</v>
-      </c>
-      <c r="C21">
-        <v>30.57000619490823</v>
       </c>
       <c r="D21">
         <v>4.106571446085944</v>
       </c>
       <c r="E21">
-        <v>15.71844964228073</v>
+        <v>19.7326138799894</v>
       </c>
       <c r="F21">
         <v>64.54893647772987</v>
       </c>
       <c r="G21">
-        <v>19.7326138799894</v>
+        <v>15.71844964228073</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>30.1665404996215</v>
+      </c>
+      <c r="C22">
         <v>36.71461014383043</v>
-      </c>
-      <c r="C22">
-        <v>30.1665404996215</v>
       </c>
       <c r="D22">
         <v>2.723711340206186</v>
       </c>
       <c r="E22">
-        <v>22.00045361760036</v>
+        <v>18.07666137446133</v>
       </c>
       <c r="F22">
         <v>59.92288500793831</v>
       </c>
       <c r="G22">
-        <v>18.07666137446133</v>
+        <v>22.00045361760036</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.46407247271979</v>
+      </c>
+      <c r="C23">
         <v>26.24562487131974</v>
-      </c>
-      <c r="C23">
-        <v>28.46407247271979</v>
       </c>
       <c r="D23">
         <v>3.810158854677388</v>
       </c>
       <c r="E23">
-        <v>16.96443424160761</v>
+        <v>18.39837641813887</v>
       </c>
       <c r="F23">
-        <v>64.63718934025351</v>
+        <v>64.63718934025353</v>
       </c>
       <c r="G23">
-        <v>18.39837641813887</v>
+        <v>16.96443424160762</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.63609525683921</v>
+      </c>
+      <c r="C24">
         <v>30.29587351571213</v>
-      </c>
-      <c r="C24">
-        <v>28.63609525683921</v>
       </c>
       <c r="D24">
         <v>3.300779558250325</v>
       </c>
       <c r="E24">
-        <v>19.0621646165277</v>
+        <v>18.01783208123503</v>
       </c>
       <c r="F24">
         <v>62.92000330223727</v>
       </c>
       <c r="G24">
-        <v>18.01783208123503</v>
+        <v>19.0621646165277</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.33795348348822</v>
+      </c>
+      <c r="C25">
         <v>30.41948863338059</v>
-      </c>
-      <c r="C25">
-        <v>29.33795348348822</v>
       </c>
       <c r="D25">
         <v>3.287366240938902</v>
       </c>
       <c r="E25">
-        <v>19.04104637023892</v>
+        <v>18.36406060008545</v>
       </c>
       <c r="F25">
         <v>62.59489302967565</v>
       </c>
       <c r="G25">
-        <v>18.36406060008545</v>
+        <v>19.04104637023892</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.48385983083031</v>
+      </c>
+      <c r="C26">
         <v>27.4469186949767</v>
-      </c>
-      <c r="C26">
-        <v>29.48385983083031</v>
       </c>
       <c r="D26">
         <v>3.643396226415094</v>
       </c>
       <c r="E26">
-        <v>17.48982510174898</v>
+        <v>18.78781212187878</v>
       </c>
       <c r="F26">
         <v>63.72236277637224</v>
       </c>
       <c r="G26">
-        <v>18.78781212187878</v>
+        <v>17.48982510174898</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>29.01388888888889</v>
+      </c>
+      <c r="C27">
         <v>27.61111111111111</v>
-      </c>
-      <c r="C27">
-        <v>29.01388888888889</v>
       </c>
       <c r="D27">
         <v>3.621730382293763</v>
       </c>
       <c r="E27">
-        <v>17.62880198634388</v>
+        <v>18.52443025627383</v>
       </c>
       <c r="F27">
         <v>63.84676775738228</v>
       </c>
       <c r="G27">
-        <v>18.52443025627383</v>
+        <v>17.62880198634388</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.62762237762238</v>
+      </c>
+      <c r="C28">
         <v>46.37237762237762</v>
-      </c>
-      <c r="C28">
-        <v>28.62762237762238</v>
       </c>
       <c r="D28">
         <v>2.156456173421301</v>
       </c>
       <c r="E28">
-        <v>26.49850149850149</v>
+        <v>16.35864135864136</v>
       </c>
       <c r="F28">
         <v>57.14285714285715</v>
       </c>
       <c r="G28">
-        <v>16.35864135864136</v>
+        <v>26.49850149850149</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.36222858104696</v>
+      </c>
+      <c r="C29">
         <v>37.14862817707456</v>
-      </c>
-      <c r="C29">
-        <v>28.36222858104696</v>
       </c>
       <c r="D29">
         <v>2.691889442682374</v>
       </c>
       <c r="E29">
-        <v>22.44482863825893</v>
+        <v>17.13617410759687</v>
       </c>
       <c r="F29">
         <v>60.41899725414421</v>
       </c>
       <c r="G29">
-        <v>17.13617410759687</v>
+        <v>22.44482863825893</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>28.62547288776797</v>
+      </c>
+      <c r="C30">
         <v>36.31778058007566</v>
-      </c>
-      <c r="C30">
-        <v>28.62547288776797</v>
       </c>
       <c r="D30">
         <v>2.753472222222222</v>
       </c>
       <c r="E30">
-        <v>22.01834862385321</v>
+        <v>17.35474006116208</v>
       </c>
       <c r="F30">
         <v>60.6269113149847</v>
       </c>
       <c r="G30">
-        <v>17.35474006116208</v>
+        <v>22.01834862385321</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>31.28171903682108</v>
+      </c>
+      <c r="C31">
         <v>31.15214339704135</v>
-      </c>
-      <c r="C31">
-        <v>31.28171903682108</v>
       </c>
       <c r="D31">
         <v>3.210051993067591</v>
       </c>
       <c r="E31">
-        <v>19.17835538124044</v>
+        <v>19.25812670345011</v>
       </c>
       <c r="F31">
         <v>61.56351791530945</v>
       </c>
       <c r="G31">
-        <v>19.25812670345011</v>
+        <v>19.17835538124044</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>29.38467978233571</v>
+      </c>
+      <c r="C32">
         <v>32.94265383005441</v>
-      </c>
-      <c r="C32">
-        <v>29.38467978233571</v>
       </c>
       <c r="D32">
         <v>3.035578144853876</v>
       </c>
       <c r="E32">
-        <v>20.293965961836</v>
+        <v>18.10211449200619</v>
       </c>
       <c r="F32">
         <v>61.60391954615782</v>
       </c>
       <c r="G32">
-        <v>18.10211449200619</v>
+        <v>20.293965961836</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>27.47835174679009</v>
+      </c>
+      <c r="C33">
         <v>37.84711854284861</v>
-      </c>
-      <c r="C33">
-        <v>27.47835174679009</v>
       </c>
       <c r="D33">
         <v>2.642209072978304</v>
       </c>
       <c r="E33">
-        <v>22.89249108231363</v>
+        <v>16.62076127692238</v>
       </c>
       <c r="F33">
         <v>60.48674764076399</v>
       </c>
       <c r="G33">
-        <v>16.62076127692238</v>
+        <v>22.89249108231363</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>44.1268316118184</v>
+      </c>
+      <c r="C34">
         <v>18.90463607975018</v>
-      </c>
-      <c r="C34">
-        <v>44.1268316118184</v>
       </c>
       <c r="D34">
         <v>5.289707750952986</v>
       </c>
       <c r="E34">
-        <v>11.59569765728599</v>
+        <v>27.06645056726094</v>
       </c>
       <c r="F34">
         <v>61.33785177545307</v>
       </c>
       <c r="G34">
-        <v>27.06645056726094</v>
+        <v>11.59569765728599</v>
       </c>
     </row>
   </sheetData>
